--- a/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>361.86</v>
+        <v>352.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11026.77</v>
+        <v>10745.2</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>120.15</v>
+        <v>117.08</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16339.11</v>
+        <v>15921.88</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4223.32</v>
+        <v>4115.47</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16965.99</v>
+        <v>16532.75</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1591.22</v>
+        <v>1550.58</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>172.31</v>
+        <v>167.91</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1649.1</v>
+        <v>1606.99</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1526.81</v>
+        <v>1487.82</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>303.6</v>
+        <v>297.67</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1352.67</v>
+        <v>1326.28</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>88.04000000000001</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4227.09</v>
+        <v>4144.64</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6236.47</v>
+        <v>6114.84</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>33646.13</v>
+        <v>32989.88</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>856.1900000000001</v>
+        <v>839.49</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1225.05</v>
+        <v>1201.15</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1494.02</v>
+        <v>1464.88</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4743.69</v>
+        <v>4651.17</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1972.19</v>
+        <v>1933.73</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3199.07</v>
+        <v>3136.67</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>33929.6</v>
+        <v>33267.82</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1167.83</v>
+        <v>1145.06</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>410.31</v>
+        <v>402.3</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>11767.19</v>
+        <v>11537.68</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6174.5</v>
+        <v>6054.07</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>194.93</v>
+        <v>191.13</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>440.06</v>
+        <v>429.77</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3173.31</v>
+        <v>3099.07</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>473.33</v>
+        <v>462.25</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>660.09</v>
+        <v>644.65</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3409.79</v>
+        <v>3330.02</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>183.29</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10631.23</v>
+        <v>10382.52</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>435.23</v>
+        <v>425.05</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>971.96</v>
+        <v>949.22</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>880.42</v>
+        <v>859.8200000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>430.79</v>
+        <v>420.71</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>795.61</v>
+        <v>777</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>508.87</v>
+        <v>496.96</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>72.63</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>421.36</v>
+        <v>411.51</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>440.21</v>
+        <v>429.91</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>132.06</v>
+        <v>128.97</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>383.4</v>
+        <v>374.43</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>79.56</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>76329.88</v>
+        <v>74544.27</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2544.33</v>
+        <v>2484.81</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8454.17</v>
+        <v>8256.4</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>290.66</v>
+        <v>286.49</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1268.13</v>
+        <v>1249.95</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1023.06</v>
+        <v>1008.4</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2812.76</v>
+        <v>2772.45</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>140.01</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1972.19</v>
+        <v>1943.92</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>291.59</v>
+        <v>287.41</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>175.46</v>
+        <v>172.95</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>986.1</v>
+        <v>971.96</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>222.02</v>
+        <v>218.83</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>788.88</v>
+        <v>777.5700000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>197.22</v>
+        <v>194.39</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>292.4</v>
+        <v>288.2</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>284.32</v>
+        <v>280.24</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>10632.77</v>
+        <v>10480.37</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>82.91</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>411.94</v>
+        <v>406.03</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>463.98</v>
+        <v>457.33</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>150.77</v>
+        <v>148.61</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>13187.71</v>
+        <v>12998.69</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>271.88</v>
+        <v>267.98</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2422.88</v>
+        <v>2388.15</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1005.62</v>
+        <v>991.2</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>118.47</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>189.55</v>
+        <v>186.83</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>110.88</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>118.47</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>180.07</v>
+        <v>177.49</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>331.71</v>
+        <v>326.95</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2651.23</v>
+        <v>2613.23</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>126.05</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>379.09</v>
+        <v>373.66</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>132.68</v>
+        <v>130.78</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>726.35</v>
+        <v>715.9299999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10784.07</v>
+        <v>10629.5</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>66.03</v>
+        <v>65.08</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>167.28</v>
+        <v>164.88</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>132.06</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>16951.82</v>
+        <v>16708.85</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1064.98</v>
+        <v>1049.72</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2391.88</v>
+        <v>2361.52</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6729.28</v>
+        <v>6643.87</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1048.83</v>
+        <v>1035.52</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1174.43</v>
+        <v>1159.52</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>394.44</v>
+        <v>389.43</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3107.04</v>
+        <v>3067.6</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4441.87</v>
+        <v>4385.49</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1130.7</v>
+        <v>1116.35</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>507.25</v>
+        <v>500.81</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2921.27</v>
+        <v>2884.19</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>659.1</v>
+        <v>650.74</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>768.95</v>
+        <v>759.1900000000001</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>665.03</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>17471.57</v>
+        <v>17249.81</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1485.13</v>
+        <v>1466.28</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>288.36</v>
+        <v>284.7</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>369.4</v>
+        <v>364.71</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>81.98</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>249.72</v>
+        <v>246.55</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>9732.35</v>
+        <v>9592.110000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>379.66</v>
+        <v>374.19</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2568.56</v>
+        <v>2531.55</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>613.87</v>
+        <v>605.02</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>391.75</v>
+        <v>386.1</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>504.96</v>
+        <v>497.69</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1958.73</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1750.07</v>
+        <v>1724.85</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>506.17</v>
+        <v>498.88</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>68.86</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>557.33</v>
+        <v>549.3</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>264.37</v>
+        <v>260.56</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>14128.84</v>
+        <v>13925.24</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3164.24</v>
+        <v>3118.65</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6276.13</v>
+        <v>6185.69</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4805.96</v>
+        <v>4736.7</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>490.02</v>
+        <v>482.96</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>153.94</v>
+        <v>151.72</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>993.5</v>
+        <v>979.1799999999999</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>9477.290000000001</v>
+        <v>9340.719999999999</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2640.37</v>
+        <v>2602.33</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>136.51</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>98.61</v>
+        <v>97.19</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>500.14</v>
+        <v>492.94</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>934.27</v>
+        <v>920.8</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>9750.57</v>
+        <v>9610.059999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>934.1900000000001</v>
+        <v>920.72</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1400.96</v>
+        <v>1380.77</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>121.16</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1626.33</v>
+        <v>1605.31</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4563.64</v>
+        <v>4504.66</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1673.6</v>
+        <v>1651.97</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>9095.98</v>
+        <v>8978.42</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>437.52</v>
+        <v>431.86</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5284.67</v>
+        <v>5216.37</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5464.18</v>
+        <v>5393.56</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>292.4</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3518.71</v>
+        <v>3473.24</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>242.35</v>
+        <v>239.22</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1724.01</v>
+        <v>1701.72</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>12364.5</v>
+        <v>12204.7</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3410.82</v>
+        <v>3366.73</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11456.08</v>
+        <v>11308.02</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>9864.93</v>
+        <v>9737.43</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>255.24</v>
+        <v>251.94</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6728.45</v>
+        <v>6641.48</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1731.57</v>
+        <v>1709.19</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1433.71</v>
+        <v>1415.18</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7094.51</v>
+        <v>7002.81</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>342.26</v>
+        <v>337.84</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>480.95</v>
+        <v>474.74</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1583.77</v>
+        <v>1563.3</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7003.03</v>
+        <v>6912.52</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>168.01</v>
+        <v>165.84</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>496.58</v>
+        <v>490.16</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>102.98</v>
+        <v>101.65</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>845.42</v>
+        <v>834.49</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>219.7</v>
+        <v>216.86</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1822.02</v>
+        <v>1798.47</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>291.72</v>
+        <v>287.95</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1676.03</v>
+        <v>1654.36</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1744.68</v>
+        <v>1722.13</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1493.83</v>
+        <v>1474.52</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>557.33</v>
+        <v>550.13</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>4853.24</v>
+        <v>4790.51</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5502.48</v>
+        <v>5431.36</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>294.66</v>
+        <v>290.85</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>628.41</v>
+        <v>620.29</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6381.02</v>
+        <v>6298.55</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>500.1</v>
+        <v>493.64</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>11097.72</v>
+        <v>10954.29</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>179.03</v>
+        <v>176.72</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>130.25</v>
+        <v>128.56</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>781.47</v>
+        <v>771.37</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1042.7</v>
+        <v>1029.23</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1562.95</v>
+        <v>1542.75</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>86.75</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1023.12</v>
+        <v>1009.89</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>212.81</v>
+        <v>210.06</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>840.03</v>
+        <v>829.1799999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1942.52</v>
+        <v>1938.7</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>18840.15</v>
+        <v>18803.05</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3436.53</v>
+        <v>3429.76</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>148.86</v>
+        <v>148.57</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1580.84</v>
+        <v>1577.72</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5637.1</v>
+        <v>5626</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>222.4</v>
+        <v>221.96</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>385.68</v>
+        <v>384.92</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>906.1900000000001</v>
+        <v>904.41</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2979.16</v>
+        <v>2973.29</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>10130.91</v>
+        <v>10110.96</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>291.39</v>
+        <v>290.81</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>484.63</v>
+        <v>483.68</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3964.31</v>
+        <v>3956.5</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>270.59</v>
+        <v>270.05</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>75.17</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>6607.55</v>
+        <v>6594.54</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>27774.05</v>
+        <v>27719.35</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>575.1</v>
+        <v>573.97</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>84841.95</v>
+        <v>84674.86</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5719.03</v>
+        <v>5707.77</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>924.4400000000001</v>
+        <v>922.62</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2605.01</v>
+        <v>2599.88</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2994.29</v>
+        <v>2988.39</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>255.24</v>
+        <v>254.74</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>811.98</v>
+        <v>810.38</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1235.82</v>
+        <v>1233.38</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>5660.36</v>
+        <v>5649.21</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>55.5</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>751.72</v>
+        <v>750.24</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1409.48</v>
+        <v>1406.7</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>163.7</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1248.48</v>
+        <v>1246.02</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>117.52</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>117.52</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>163.7</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2023.07</v>
+        <v>2019.08</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>340.32</v>
+        <v>339.65</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>33929.56</v>
+        <v>33862.74</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>437.52</v>
+        <v>436.66</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4644.41</v>
+        <v>4635.26</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7303.05</v>
+        <v>7288.67</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1114.66</v>
+        <v>1112.46</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>275.43</v>
+        <v>274.89</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>171.24</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>5256.93</v>
+        <v>5246.58</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>710.9</v>
+        <v>709.5</v>
       </c>
     </row>
     <row r="239">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3329.84</v>
+        <v>3329.86</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>848.11</v>
+        <v>848.12</v>
       </c>
     </row>
     <row r="242">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>143.77</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>49929.4</v>
+        <v>49929.73</v>
       </c>
     </row>
     <row r="246">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>17671.65</v>
+        <v>17671.76</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1958.73</v>
+        <v>1958.74</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1372.05</v>
+        <v>1372.06</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>711.64</v>
+        <v>711.65</v>
       </c>
     </row>
     <row r="251">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1371.11</v>
+        <v>1371.12</v>
       </c>
     </row>
     <row r="253">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4310.4</v>
+        <v>4310.43</v>
       </c>
     </row>
     <row r="255">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13238.57</v>
+        <v>13238.66</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>25449.41</v>
+        <v>25449.58</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>595.5599999999999</v>
+        <v>595.5700000000001</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>67875.89</v>
+        <v>67876.33</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5030.62</v>
+        <v>5030.66</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>230.87</v>
+        <v>230.88</v>
       </c>
     </row>
     <row r="262">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5917.92</v>
+        <v>5917.96</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2471.63</v>
+        <v>2471.65</v>
       </c>
     </row>
     <row r="265">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>3167.17</v>
+        <v>3167.19</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1401.4</v>
+        <v>1401.41</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4307.86</v>
+        <v>4307.89</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1244.37</v>
+        <v>1244.38</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>339.24</v>
+        <v>339.25</v>
       </c>
     </row>
     <row r="272">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>122.15</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1722.07</v>
+        <v>1722.08</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1194.76</v>
+        <v>1194.77</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>3959.15</v>
+        <v>3959.17</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>16968.87</v>
+        <v>16968.98</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3680.08</v>
+        <v>3685.19</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3959.04</v>
+        <v>3964.54</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1750.07</v>
+        <v>1752.5</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>11297.14</v>
+        <v>11312.82</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>11311.56</v>
+        <v>11327.27</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1242.95</v>
+        <v>1244.68</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>19231.5</v>
+        <v>19258.2</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2262.29</v>
+        <v>2265.43</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5090.66</v>
+        <v>5097.73</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>969.27</v>
+        <v>970.61</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>980.7</v>
+        <v>982.0599999999999</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>6774.62</v>
+        <v>6784.02</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>247.97</v>
+        <v>248.32</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>14077.39</v>
+        <v>14096.93</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>218.76</v>
+        <v>219.06</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>459.06</v>
+        <v>459.69</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1144.03</v>
+        <v>1145.62</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>10533.12</v>
+        <v>10547.75</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>506.17</v>
+        <v>506.88</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>234.91</v>
+        <v>235.24</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3623.52</v>
+        <v>3628.55</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>4510.71</v>
+        <v>4516.97</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>20348.79</v>
+        <v>20377.05</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>714.03</v>
+        <v>715.02</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>187.93</v>
+        <v>188.19</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>607.41</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1295.1</v>
+        <v>1296.9</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>248.38</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>509.27</v>
+        <v>509.98</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2742.22</v>
+        <v>2746.03</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>4792.49</v>
+        <v>4799.15</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>243.66</v>
+        <v>244</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>8400.33</v>
+        <v>8411.99</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1389.82</v>
+        <v>1391.75</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>149.03</v>
+        <v>149.23</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>292.67</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>11598.91</v>
+        <v>11615.02</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>394.73</v>
+        <v>395.28</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>33937.53</v>
+        <v>33984.65</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2705.87</v>
+        <v>2709.63</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>696.66</v>
+        <v>697.63</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>7452.58</v>
+        <v>7447.48</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>287.7</v>
+        <v>287.51</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>38560.73</v>
+        <v>38534.38</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2008.27</v>
+        <v>2006.9</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>87974.92999999999</v>
+        <v>87914.83</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>338.82</v>
+        <v>338.59</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>285.93</v>
+        <v>285.74</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>320.94</v>
+        <v>320.72</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>2004.69</v>
+        <v>2003.32</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>504.02</v>
+        <v>503.68</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>280.82</v>
+        <v>280.63</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>8578.299999999999</v>
+        <v>8572.440000000001</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>320.94</v>
+        <v>320.72</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2793.68</v>
+        <v>2791.77</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1235.82</v>
+        <v>1234.97</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>712.8200000000001</v>
+        <v>712.33</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>918.11</v>
+        <v>917.49</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>470.1</v>
+        <v>469.77</v>
       </c>
     </row>
     <row r="337">
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>350.01</v>
+        <v>349.77</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>12878.35</v>
+        <v>12869.55</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>739.98</v>
+        <v>739.48</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>347.86</v>
+        <v>347.62</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>215.76</v>
+        <v>215.61</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>840.03</v>
+        <v>839.46</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>540.77</v>
+        <v>540.4</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>35893.09</v>
+        <v>35868.57</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>667.1799999999999</v>
+        <v>666.72</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>262.51</v>
+        <v>262.33</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>245.55</v>
+        <v>245.38</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>527.71</v>
+        <v>527.35</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>245.55</v>
+        <v>245.38</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>47746.89</v>
+        <v>47714.27</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>111.22</v>
+        <v>110.84</v>
       </c>
     </row>
     <row r="352">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1569</v>
+        <v>1563.62</v>
       </c>
     </row>
     <row r="353">
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>3521.27</v>
+        <v>3509.19</v>
       </c>
     </row>
     <row r="354">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>30344.5</v>
+        <v>30240.35</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>126</v>
+        <v>125.57</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>30844.58</v>
+        <v>30738.72</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>7773.42</v>
+        <v>7746.75</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>102.58</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>11510.06</v>
+        <v>11470.56</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>70.63</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1215.62</v>
+        <v>1211.45</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>107.36</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="363">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1170.65</v>
+        <v>1166.63</v>
       </c>
     </row>
     <row r="364">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>834.65</v>
+        <v>831.78</v>
       </c>
     </row>
     <row r="365">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>21471.99</v>
+        <v>21398.29</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>48133.87</v>
+        <v>47968.67</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>228.18</v>
+        <v>227.4</v>
       </c>
     </row>
     <row r="368">
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>190.62</v>
+        <v>189.97</v>
       </c>
     </row>
     <row r="369">
@@ -22964,7 +22964,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>164.45</v>
+        <v>163.89</v>
       </c>
     </row>
     <row r="370">
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>119.14</v>
+        <v>118.73</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>225.49</v>
+        <v>224.72</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>456.36</v>
+        <v>454.8</v>
       </c>
     </row>
     <row r="373">
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>27765.5</v>
+        <v>27670.21</v>
       </c>
     </row>
     <row r="374">
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2005.17</v>
+        <v>1998.29</v>
       </c>
     </row>
     <row r="375">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>185</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="376">
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>130.16</v>
+        <v>129.72</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>376.94</v>
+        <v>375.64</v>
       </c>
     </row>
     <row r="378">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>141.73</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="379">
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>141.73</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="380">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>141.73</v>
+        <v>141.24</v>
       </c>
     </row>
     <row r="381">
@@ -23696,7 +23696,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4485.56</v>
+        <v>4470.16</v>
       </c>
     </row>
     <row r="382">
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1667.14</v>
+        <v>1661.42</v>
       </c>
     </row>
     <row r="383">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>858.88</v>
+        <v>855.9299999999999</v>
       </c>
     </row>
     <row r="384">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>332.65</v>
+        <v>331.51</v>
       </c>
     </row>
     <row r="385">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>507.27</v>
+        <v>505.53</v>
       </c>
     </row>
     <row r="386">
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1369.09</v>
+        <v>1364.39</v>
       </c>
     </row>
     <row r="387">
@@ -24062,7 +24062,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>10350.18</v>
+        <v>10314.66</v>
       </c>
     </row>
     <row r="388">
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>5196.36</v>
+        <v>5178.52</v>
       </c>
     </row>
     <row r="389">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3129.23</v>
+        <v>3118.49</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>684.55</v>
+        <v>682.2</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1762.86</v>
+        <v>1756.81</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1962.36</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>85.89</v>
+        <v>85.43000000000001</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4288.06</v>
+        <v>4265.41</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>564.1900000000001</v>
+        <v>561.21</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2685.68</v>
+        <v>2671.49</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>415.71</v>
+        <v>413.51</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>17177.59</v>
+        <v>17086.85</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1130.81</v>
+        <v>1124.84</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2766.32</v>
+        <v>2751.71</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1688.12</v>
+        <v>1679.2</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>343.55</v>
+        <v>341.74</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>9089.58</v>
+        <v>9041.57</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>644.16</v>
+        <v>640.76</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>515.33</v>
+        <v>512.61</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>257.66</v>
+        <v>256.3</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>16953.86</v>
+        <v>16864.3</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>359.65</v>
+        <v>357.75</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1137.49</v>
+        <v>1131.48</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>625.99</v>
+        <v>622.6799999999999</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>210.01</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>672.4299999999999</v>
+        <v>668.88</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>790.48</v>
+        <v>786.3</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>149.28</v>
+        <v>148.49</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>243.04</v>
+        <v>241.76</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>901.39</v>
+        <v>896.63</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>244.34</v>
+        <v>243.05</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>195.47</v>
+        <v>194.44</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1958.73</v>
+        <v>1948.38</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>929.96</v>
+        <v>925.05</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1958.25</v>
+        <v>1947.9</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5594.49</v>
+        <v>5564.94</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>4561.32</v>
+        <v>4537.23</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>5088.66</v>
+        <v>5061.78</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>4501.71</v>
+        <v>4477.93</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>154.6</v>
+        <v>153.78</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>320.94</v>
+        <v>319.24</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>13180</v>
+        <v>13110.38</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1361.84</v>
+        <v>1354.64</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>2300.89</v>
+        <v>2288.74</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>80.23</v>
+        <v>79.81</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>668.17</v>
+        <v>664.64</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>336.01</v>
+        <v>334.24</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>767.0700000000001</v>
+        <v>763.02</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>714.84</v>
+        <v>711.0599999999999</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>166.71</v>
+        <v>165.83</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1534.67</v>
+        <v>1526.57</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>69.45999999999999</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1308.56</v>
+        <v>1301.65</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1443.76</v>
+        <v>1436.13</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>7683.28</v>
+        <v>7642.69</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>254.7</v>
+        <v>253.36</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>138.93</v>
+        <v>138.19</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>435.31</v>
+        <v>433.01</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>4914.25</v>
+        <v>4883.46</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>351.36</v>
+        <v>349.16</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>193.25</v>
+        <v>192.04</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>382.24</v>
+        <v>379.85</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>920.8</v>
+        <v>915.03</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>1852.38</v>
+        <v>1840.77</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>6563.95</v>
+        <v>6522.81</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>26407.45</v>
+        <v>26241.96</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>280.82</v>
+        <v>279.06</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>15837.73</v>
+        <v>15738.48</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>14763.78</v>
+        <v>14671.26</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>11312.6</v>
+        <v>11241.71</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>8214.549999999999</v>
+        <v>8163.07</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>774.2</v>
+        <v>769.35</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1413.52</v>
+        <v>1404.66</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>630.02</v>
+        <v>626.08</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>3585.73</v>
+        <v>3563.26</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>9579.27</v>
+        <v>9519.24</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1837.77</v>
+        <v>1826.26</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1109.02</v>
+        <v>1102.08</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>9474.6</v>
+        <v>9415.23</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1203.51</v>
+        <v>1195.97</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>766.8</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>303.7</v>
+        <v>301.8</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>328.9</v>
+        <v>326.84</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>767.42</v>
+        <v>762.61</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>7883.92</v>
+        <v>7834.51</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>138.93</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>928.29</v>
+        <v>922.47</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>6057.68</v>
+        <v>6019.72</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>573.08</v>
+        <v>569.49</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>100.29</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>5445.67</v>
+        <v>5411.55</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>33909.43</v>
+        <v>33696.93</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>1125.06</v>
+        <v>1118.01</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>749.5700000000001</v>
+        <v>744.87</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>570.25</v>
+        <v>566.6799999999999</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>442.9</v>
+        <v>440.13</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>405.21</v>
+        <v>402.67</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>166.79</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>13913.85</v>
+        <v>14005.04</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>519.64</v>
+        <v>523.04</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>792.13</v>
+        <v>797.3200000000001</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>351.71</v>
+        <v>354.02</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>4525.44</v>
+        <v>4555.1</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>72.20999999999999</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>965.03</v>
+        <v>971.35</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>689.1900000000001</v>
+        <v>693.7</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>2262.49</v>
+        <v>2277.32</v>
       </c>
     </row>
     <row r="494">
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>17.2</v>
+        <v>17.32</v>
       </c>
     </row>
     <row r="495">
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>7301.82</v>
+        <v>7349.68</v>
       </c>
     </row>
     <row r="496">
@@ -30715,7 +30715,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>959.17</v>
+        <v>965.46</v>
       </c>
     </row>
     <row r="497">
@@ -30776,7 +30776,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1731.73</v>
+        <v>1743.08</v>
       </c>
     </row>
     <row r="498">
@@ -30837,7 +30837,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>571.87</v>
+        <v>575.62</v>
       </c>
     </row>
     <row r="499">
@@ -30898,7 +30898,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>47512.72</v>
+        <v>47824.12</v>
       </c>
     </row>
     <row r="500">
@@ -30959,7 +30959,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>425.1</v>
+        <v>427.89</v>
       </c>
     </row>
     <row r="501">
@@ -31020,7 +31020,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>147.76</v>
+        <v>148.73</v>
       </c>
     </row>
     <row r="502">
@@ -31081,7 +31081,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>3991.57</v>
+        <v>4017.73</v>
       </c>
     </row>
     <row r="503">
@@ -31142,7 +31142,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1672.66</v>
+        <v>1683.62</v>
       </c>
     </row>
     <row r="504">
@@ -31203,7 +31203,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1918.34</v>
+        <v>1930.92</v>
       </c>
     </row>
     <row r="505">
@@ -31264,7 +31264,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2144.51</v>
+        <v>2158.56</v>
       </c>
     </row>
     <row r="506">
@@ -31325,7 +31325,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>28189.56</v>
+        <v>28374.31</v>
       </c>
     </row>
     <row r="507">
@@ -31386,7 +31386,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1849.99</v>
+        <v>1862.11</v>
       </c>
     </row>
     <row r="508">
@@ -31447,7 +31447,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>16131.05</v>
+        <v>16236.77</v>
       </c>
     </row>
     <row r="509">
@@ -31508,7 +31508,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>781.88</v>
+        <v>787</v>
       </c>
     </row>
     <row r="510">
@@ -31569,7 +31569,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>14730.39</v>
+        <v>14826.93</v>
       </c>
     </row>
     <row r="511">
@@ -31630,7 +31630,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1247.13</v>
+        <v>1255.3</v>
       </c>
     </row>
     <row r="512">
@@ -31691,7 +31691,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>767.34</v>
+        <v>772.37</v>
       </c>
     </row>
     <row r="513">
@@ -31752,7 +31752,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>872.21</v>
+        <v>877.92</v>
       </c>
     </row>
     <row r="514">
@@ -31813,7 +31813,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5984.84</v>
+        <v>6024.07</v>
       </c>
     </row>
     <row r="515">
@@ -31874,7 +31874,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>435.97</v>
+        <v>438.83</v>
       </c>
     </row>
     <row r="516">
@@ -31935,7 +31935,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>644.16</v>
+        <v>648.38</v>
       </c>
     </row>
     <row r="517">
@@ -31996,7 +31996,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>133.27</v>
+        <v>134.15</v>
       </c>
     </row>
     <row r="518">
@@ -32057,7 +32057,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>4663.76</v>
+        <v>4694.32</v>
       </c>
     </row>
     <row r="519">
@@ -32118,7 +32118,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>410.32</v>
+        <v>413.01</v>
       </c>
     </row>
     <row r="520">
@@ -32179,7 +32179,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>479.25</v>
+        <v>482.39</v>
       </c>
     </row>
     <row r="521">
@@ -32240,7 +32240,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>1717.76</v>
+        <v>1729.02</v>
       </c>
     </row>
     <row r="522">
@@ -32301,7 +32301,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>3630.44</v>
+        <v>3679.32</v>
       </c>
     </row>
     <row r="523">
@@ -32362,7 +32362,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>5353.66</v>
+        <v>5425.76</v>
       </c>
     </row>
     <row r="524">
@@ -32423,7 +32423,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1235.82</v>
+        <v>1252.46</v>
       </c>
     </row>
     <row r="525">
@@ -32484,7 +32484,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>19.32</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="526">
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>8904.57</v>
+        <v>9024.49</v>
       </c>
     </row>
     <row r="527">
@@ -32606,7 +32606,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>3658.91</v>
+        <v>3708.19</v>
       </c>
     </row>
     <row r="528">
@@ -32667,7 +32667,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1174.56</v>
+        <v>1190.38</v>
       </c>
     </row>
     <row r="529">
@@ -32728,7 +32728,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>128.83</v>
+        <v>130.57</v>
       </c>
     </row>
     <row r="530">
@@ -32789,7 +32789,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>644.16</v>
+        <v>652.83</v>
       </c>
     </row>
     <row r="531">
@@ -32850,7 +32850,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>2520.1</v>
+        <v>2554.03</v>
       </c>
     </row>
     <row r="532">
@@ -32911,7 +32911,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1974.62</v>
+        <v>2001.21</v>
       </c>
     </row>
     <row r="533">
@@ -32972,7 +32972,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>13728.21</v>
+        <v>13913.08</v>
       </c>
     </row>
     <row r="534">
@@ -33033,7 +33033,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>4294.4</v>
+        <v>4352.23</v>
       </c>
     </row>
     <row r="535">
@@ -33094,7 +33094,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>565.41</v>
+        <v>573.02</v>
       </c>
     </row>
     <row r="536">
@@ -33155,7 +33155,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1140.91</v>
+        <v>1156.27</v>
       </c>
     </row>
     <row r="537">
@@ -33216,7 +33216,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>556.4400000000001</v>
+        <v>563.9400000000001</v>
       </c>
     </row>
     <row r="538">
@@ -33277,7 +33277,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1405.44</v>
+        <v>1424.37</v>
       </c>
     </row>
     <row r="539">
@@ -33338,7 +33338,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>150.3</v>
+        <v>152.33</v>
       </c>
     </row>
     <row r="540">
@@ -33399,7 +33399,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2595.22</v>
+        <v>2630.16</v>
       </c>
     </row>
     <row r="541">
@@ -33460,7 +33460,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>575.22</v>
+        <v>582.97</v>
       </c>
     </row>
     <row r="542">
@@ -33521,7 +33521,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>68.86</v>
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="543">
@@ -33582,7 +33582,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>234.4</v>
+        <v>237.55</v>
       </c>
     </row>
     <row r="544">
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>22625.62</v>
+        <v>22930.3</v>
       </c>
     </row>
     <row r="545">
@@ -33704,7 +33704,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1494.29</v>
+        <v>1514.41</v>
       </c>
     </row>
     <row r="546">
@@ -33765,7 +33765,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1136.82</v>
+        <v>1152.13</v>
       </c>
     </row>
     <row r="547">
@@ -33826,7 +33826,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>575.26</v>
+        <v>583.01</v>
       </c>
     </row>
     <row r="548">
@@ -33887,7 +33887,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1025.81</v>
+        <v>1039.62</v>
       </c>
     </row>
     <row r="549">
@@ -33948,7 +33948,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1696.58</v>
+        <v>1719.43</v>
       </c>
     </row>
     <row r="550">
@@ -34009,7 +34009,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1413.82</v>
+        <v>1432.86</v>
       </c>
     </row>
     <row r="551">
@@ -34070,7 +34070,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>210.01</v>
+        <v>212.84</v>
       </c>
     </row>
     <row r="552">
@@ -34131,7 +34131,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>4509.79</v>
+        <v>4570.52</v>
       </c>
     </row>
     <row r="553">
@@ -34192,7 +34192,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>885.8</v>
+        <v>897.73</v>
       </c>
     </row>
     <row r="554">
@@ -34253,7 +34253,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>383.4</v>
+        <v>388.56</v>
       </c>
     </row>
     <row r="555">
@@ -34314,7 +34314,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>504.02</v>
+        <v>510.81</v>
       </c>
     </row>
     <row r="556">
@@ -34375,7 +34375,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>165.26</v>
+        <v>167.49</v>
       </c>
     </row>
     <row r="557">
@@ -34436,7 +34436,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>740.95</v>
+        <v>752.23</v>
       </c>
     </row>
     <row r="558">
@@ -34497,7 +34497,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>153.47</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="559">
@@ -34558,7 +34558,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>575.5</v>
+        <v>584.26</v>
       </c>
     </row>
     <row r="560">
@@ -34619,7 +34619,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>119.14</v>
+        <v>120.95</v>
       </c>
     </row>
     <row r="561">
@@ -34680,7 +34680,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1696.5</v>
+        <v>1722.33</v>
       </c>
     </row>
     <row r="562">
@@ -34741,7 +34741,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>1696.5</v>
+        <v>1722.33</v>
       </c>
     </row>
     <row r="563">
@@ -34802,7 +34802,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>33937.8</v>
+        <v>34454.47</v>
       </c>
     </row>
     <row r="564">
@@ -34863,7 +34863,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>802.34</v>
+        <v>814.55</v>
       </c>
     </row>
     <row r="565">
@@ -34924,7 +34924,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>2378.75</v>
+        <v>2414.96</v>
       </c>
     </row>
     <row r="566">
@@ -34985,7 +34985,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>469.83</v>
+        <v>476.98</v>
       </c>
     </row>
     <row r="567">
@@ -35046,7 +35046,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>6264.28</v>
+        <v>6359.65</v>
       </c>
     </row>
     <row r="568">
@@ -35107,7 +35107,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>463.09</v>
+        <v>470.15</v>
       </c>
     </row>
     <row r="569">
@@ -35168,7 +35168,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>578.88</v>
+        <v>587.7</v>
       </c>
     </row>
     <row r="570">
@@ -35229,7 +35229,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1470.53</v>
+        <v>1492.92</v>
       </c>
     </row>
     <row r="571">
@@ -35290,7 +35290,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>5255.86</v>
+        <v>5335.87</v>
       </c>
     </row>
     <row r="572">
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>498.1</v>
+        <v>505.68</v>
       </c>
     </row>
     <row r="573">
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>834.4299999999999</v>
+        <v>847.14</v>
       </c>
     </row>
     <row r="574">
@@ -35473,7 +35473,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>1197.25</v>
+        <v>1215.48</v>
       </c>
     </row>
     <row r="575">
@@ -35534,7 +35534,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1112.24</v>
+        <v>1129.17</v>
       </c>
     </row>
     <row r="576">
@@ -35595,7 +35595,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>2348.32</v>
+        <v>2384.07</v>
       </c>
     </row>
     <row r="577">
@@ -35656,7 +35656,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>247.16</v>
+        <v>250.93</v>
       </c>
     </row>
     <row r="578">
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>401.17</v>
+        <v>407.28</v>
       </c>
     </row>
     <row r="579">
@@ -35778,7 +35778,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>5656.55</v>
+        <v>5742.67</v>
       </c>
     </row>
     <row r="580">
@@ -35839,7 +35839,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>197.41</v>
+        <v>200.41</v>
       </c>
     </row>
     <row r="581">
@@ -35900,7 +35900,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>9910.77</v>
+        <v>10061.65</v>
       </c>
     </row>
     <row r="582">
@@ -35961,7 +35961,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>515.33</v>
+        <v>523.17</v>
       </c>
     </row>
     <row r="583">
@@ -36022,7 +36022,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1179.68</v>
+        <v>1197.64</v>
       </c>
     </row>
     <row r="584">
@@ -36083,7 +36083,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>947.73</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="585">
@@ -36144,7 +36144,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2255.06</v>
+        <v>2289.39</v>
       </c>
     </row>
     <row r="586">
@@ -36205,7 +36205,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>384.95</v>
+        <v>390.81</v>
       </c>
     </row>
     <row r="587">
@@ -36266,7 +36266,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>498.1</v>
+        <v>505.68</v>
       </c>
     </row>
     <row r="588">
@@ -36327,7 +36327,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>262.25</v>
+        <v>266.24</v>
       </c>
     </row>
     <row r="589">
@@ -36388,7 +36388,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>102.58</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="590">
@@ -36449,7 +36449,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>240.7</v>
+        <v>244.37</v>
       </c>
     </row>
     <row r="591">
@@ -36510,7 +36510,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>230.2</v>
+        <v>233.71</v>
       </c>
     </row>
     <row r="592">
@@ -36571,7 +36571,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>3745.9</v>
+        <v>3802.93</v>
       </c>
     </row>
     <row r="593">
@@ -36632,7 +36632,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>774.1799999999999</v>
+        <v>785.96</v>
       </c>
     </row>
     <row r="594">
@@ -36693,7 +36693,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>360.78</v>
+        <v>366.28</v>
       </c>
     </row>
     <row r="595">
@@ -36754,7 +36754,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>168.01</v>
+        <v>172.09</v>
       </c>
     </row>
     <row r="596">
@@ -36815,7 +36815,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>186.77</v>
+        <v>191.31</v>
       </c>
     </row>
     <row r="597">
@@ -36876,7 +36876,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>1623.05</v>
+        <v>1662.52</v>
       </c>
     </row>
     <row r="598">
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>533.1</v>
+        <v>546.0599999999999</v>
       </c>
     </row>
     <row r="599">
@@ -36998,7 +36998,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>4575.89</v>
+        <v>4687.16</v>
       </c>
     </row>
     <row r="600">
@@ -37059,7 +37059,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>233.61</v>
+        <v>239.29</v>
       </c>
     </row>
     <row r="601">
@@ -37120,7 +37120,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>823.88</v>
+        <v>843.91</v>
       </c>
     </row>
     <row r="602">
@@ -37181,7 +37181,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>429.44</v>
+        <v>439.88</v>
       </c>
     </row>
     <row r="603">
@@ -37242,7 +37242,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1696.58</v>
+        <v>1737.84</v>
       </c>
     </row>
     <row r="604">
@@ -37303,7 +37303,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2573.41</v>
+        <v>2635.99</v>
       </c>
     </row>
     <row r="605">
@@ -37364,7 +37364,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>4307.86</v>
+        <v>4412.62</v>
       </c>
     </row>
     <row r="606">
@@ -37425,7 +37425,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>1140.37</v>
+        <v>1168.1</v>
       </c>
     </row>
     <row r="607">
@@ -37486,7 +37486,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>2955.36</v>
+        <v>3027.23</v>
       </c>
     </row>
     <row r="608">
@@ -37547,7 +37547,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>5813.78</v>
+        <v>5955.16</v>
       </c>
     </row>
     <row r="609">
@@ -37608,7 +37608,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>882.03</v>
+        <v>903.48</v>
       </c>
     </row>
     <row r="610">
@@ -37669,7 +37669,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>767.34</v>
+        <v>786</v>
       </c>
     </row>
     <row r="611">
@@ -37730,7 +37730,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>215.39</v>
+        <v>220.63</v>
       </c>
     </row>
     <row r="612">
@@ -37791,7 +37791,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>613.87</v>
+        <v>628.8</v>
       </c>
     </row>
     <row r="613">
@@ -37852,7 +37852,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>128.43</v>
+        <v>131.55</v>
       </c>
     </row>
     <row r="614">
@@ -37913,7 +37913,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>8226.610000000001</v>
+        <v>8426.66</v>
       </c>
     </row>
     <row r="615">
@@ -37974,7 +37974,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>738.8</v>
+        <v>756.76</v>
       </c>
     </row>
     <row r="616">
@@ -38035,7 +38035,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1663.89</v>
+        <v>1704.35</v>
       </c>
     </row>
     <row r="617">
@@ -38096,7 +38096,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3040.01</v>
+        <v>3113.93</v>
       </c>
     </row>
     <row r="618">
@@ -38157,7 +38157,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>230.2</v>
+        <v>235.8</v>
       </c>
     </row>
     <row r="619">
@@ -38218,7 +38218,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>171.78</v>
+        <v>175.95</v>
       </c>
     </row>
     <row r="620">
@@ -38279,7 +38279,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>2419.92</v>
+        <v>2478.77</v>
       </c>
     </row>
     <row r="621">
@@ -38340,7 +38340,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>4760.32</v>
+        <v>4876.08</v>
       </c>
     </row>
     <row r="622">
@@ -38401,7 +38401,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>233.23</v>
+        <v>238.9</v>
       </c>
     </row>
     <row r="623">
@@ -38462,7 +38462,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>70.47</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="624">
@@ -38523,7 +38523,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1026.21</v>
+        <v>1051.17</v>
       </c>
     </row>
     <row r="625">
@@ -38584,7 +38584,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2147.2</v>
+        <v>2199.41</v>
       </c>
     </row>
     <row r="626">
@@ -38645,7 +38645,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>494.33</v>
+        <v>506.35</v>
       </c>
     </row>
     <row r="627">
@@ -38706,7 +38706,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>5902.49</v>
+        <v>6046.03</v>
       </c>
     </row>
     <row r="628">
@@ -38767,7 +38767,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>5904.32</v>
+        <v>6047.9</v>
       </c>
     </row>
     <row r="629">
@@ -38828,7 +38828,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>664.35</v>
+        <v>680.51</v>
       </c>
     </row>
     <row r="630">
@@ -38889,7 +38889,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1825.09</v>
+        <v>1869.47</v>
       </c>
     </row>
     <row r="631">
@@ -38950,7 +38950,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>4437.07</v>
+        <v>4544.97</v>
       </c>
     </row>
     <row r="632">
@@ -39011,7 +39011,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2302.01</v>
+        <v>2357.99</v>
       </c>
     </row>
     <row r="633">
@@ -39072,7 +39072,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>488.67</v>
+        <v>500.56</v>
       </c>
     </row>
     <row r="634">
@@ -39133,7 +39133,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1884.69</v>
+        <v>1930.52</v>
       </c>
     </row>
     <row r="635">
@@ -39194,7 +39194,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>194.11</v>
+        <v>198.83</v>
       </c>
     </row>
     <row r="636">
@@ -39255,7 +39255,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>7427.29</v>
+        <v>7607.9</v>
       </c>
     </row>
     <row r="637">
@@ -39316,7 +39316,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>31719.88</v>
+        <v>32491.24</v>
       </c>
     </row>
     <row r="638">
@@ -39377,7 +39377,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>36887.66</v>
+        <v>37784.69</v>
       </c>
     </row>
     <row r="639">
@@ -39438,7 +39438,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>268.57</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="640">
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2396.25</v>
+        <v>2454.52</v>
       </c>
     </row>
     <row r="641">
@@ -39560,7 +39560,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>1514.4</v>
+        <v>1552.69</v>
       </c>
     </row>
     <row r="642">
@@ -39621,7 +39621,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>20094.95</v>
+        <v>20602.95</v>
       </c>
     </row>
     <row r="643">
@@ -39682,7 +39682,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>16108.57</v>
+        <v>16515.79</v>
       </c>
     </row>
     <row r="644">
@@ -39743,7 +39743,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>663.8</v>
+        <v>680.58</v>
       </c>
     </row>
     <row r="645">
@@ -39804,7 +39804,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>102.58</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="646">
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>27529.4</v>
+        <v>28225.35</v>
       </c>
     </row>
     <row r="647">
@@ -39926,7 +39926,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2999.33</v>
+        <v>3075.16</v>
       </c>
     </row>
     <row r="648">
@@ -39987,7 +39987,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>83.45999999999999</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="649">
@@ -40048,7 +40048,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>1918.34</v>
+        <v>1966.84</v>
       </c>
     </row>
     <row r="650">
@@ -40109,7 +40109,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>4563.64</v>
+        <v>4679.01</v>
       </c>
     </row>
     <row r="651">
@@ -40170,7 +40170,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1318.2</v>
+        <v>1351.53</v>
       </c>
     </row>
     <row r="652">
@@ -40231,7 +40231,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>141.35</v>
+        <v>144.93</v>
       </c>
     </row>
     <row r="653">
@@ -40292,7 +40292,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>626.12</v>
+        <v>641.95</v>
       </c>
     </row>
     <row r="654">
@@ -40353,7 +40353,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>1341.24</v>
+        <v>1375.15</v>
       </c>
     </row>
     <row r="655">
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>5226.6</v>
+        <v>5358.73</v>
       </c>
     </row>
     <row r="656">
@@ -40475,7 +40475,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>23554.57</v>
+        <v>24150.03</v>
       </c>
     </row>
     <row r="657">
@@ -40536,7 +40536,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>783.49</v>
+        <v>803.3</v>
       </c>
     </row>
     <row r="658">
@@ -40597,7 +40597,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>1695.65</v>
+        <v>1738.51</v>
       </c>
     </row>
     <row r="659">
@@ -40658,7 +40658,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>475.21</v>
+        <v>487.22</v>
       </c>
     </row>
     <row r="660">
@@ -40719,7 +40719,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>701.78</v>
+        <v>719.52</v>
       </c>
     </row>
     <row r="661">
@@ -40780,7 +40780,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>375.59</v>
+        <v>385.09</v>
       </c>
     </row>
     <row r="662">
@@ -40841,7 +40841,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>61790.86</v>
+        <v>63352.94</v>
       </c>
     </row>
     <row r="663">
@@ -40902,7 +40902,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>504.02</v>
+        <v>516.76</v>
       </c>
     </row>
     <row r="664">
@@ -40963,7 +40963,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>214.72</v>
+        <v>220.15</v>
       </c>
     </row>
     <row r="665">
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>164.91</v>
+        <v>169.08</v>
       </c>
     </row>
     <row r="666">
@@ -41085,7 +41085,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>3639.8</v>
+        <v>3731.81</v>
       </c>
     </row>
     <row r="667">
@@ -41146,7 +41146,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>4303.08</v>
+        <v>4411.86</v>
       </c>
     </row>
     <row r="668">
@@ -41207,7 +41207,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>237.61</v>
+        <v>243.61</v>
       </c>
     </row>
     <row r="669">
@@ -41268,7 +41268,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>258.35</v>
+        <v>266.18</v>
       </c>
     </row>
     <row r="670">
@@ -41329,7 +41329,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2171.72</v>
+        <v>2237.57</v>
       </c>
     </row>
     <row r="671">
@@ -41390,7 +41390,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>452.44</v>
+        <v>466.16</v>
       </c>
     </row>
     <row r="672">
@@ -41451,7 +41451,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>959.38</v>
+        <v>988.47</v>
       </c>
     </row>
     <row r="673">
@@ -41512,7 +41512,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>107.51</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="674">
@@ -41573,7 +41573,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1288.32</v>
+        <v>1327.39</v>
       </c>
     </row>
     <row r="675">
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>600.95</v>
+        <v>619.17</v>
       </c>
     </row>
     <row r="676">
@@ -41695,7 +41695,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>17177.59</v>
+        <v>17698.47</v>
       </c>
     </row>
     <row r="677">
@@ -41756,7 +41756,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>996.1900000000001</v>
+        <v>1026.4</v>
       </c>
     </row>
     <row r="678">
@@ -41817,7 +41817,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>79181.12</v>
+        <v>81582.14</v>
       </c>
     </row>
     <row r="679">
@@ -41878,7 +41878,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>383.67</v>
+        <v>395.3</v>
       </c>
     </row>
     <row r="680">
@@ -41939,7 +41939,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>344.81</v>
+        <v>355.27</v>
       </c>
     </row>
     <row r="681">
@@ -42000,7 +42000,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>3211.04</v>
+        <v>3308.41</v>
       </c>
     </row>
     <row r="682">
@@ -42061,7 +42061,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>149.43</v>
+        <v>153.96</v>
       </c>
     </row>
     <row r="683">
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>498.1</v>
+        <v>513.2</v>
       </c>
     </row>
     <row r="684">
@@ -42183,7 +42183,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>1126.69</v>
+        <v>1160.86</v>
       </c>
     </row>
     <row r="685">
@@ -42244,7 +42244,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>4145.96</v>
+        <v>4271.67</v>
       </c>
     </row>
     <row r="686">
@@ -42305,7 +42305,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>8983.370000000001</v>
+        <v>9255.77</v>
       </c>
     </row>
     <row r="687">
@@ -42366,7 +42366,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1993.87</v>
+        <v>2054.33</v>
       </c>
     </row>
     <row r="688">
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>856.72</v>
+        <v>882.7</v>
       </c>
     </row>
     <row r="689">
@@ -42488,7 +42488,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>6787.23</v>
+        <v>6993.04</v>
       </c>
     </row>
     <row r="690">
@@ -42549,7 +42549,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>120.4</v>
+        <v>124.06</v>
       </c>
     </row>
     <row r="691">
@@ -42610,7 +42610,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>12254.89</v>
+        <v>12626.5</v>
       </c>
     </row>
     <row r="692">
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>383.57</v>
+        <v>395.2</v>
       </c>
     </row>
     <row r="693">
@@ -42732,7 +42732,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>13006.88</v>
+        <v>13401.29</v>
       </c>
     </row>
     <row r="694">
@@ -42793,7 +42793,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>4016.52</v>
+        <v>4138.31</v>
       </c>
     </row>
     <row r="695">
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>12952.54</v>
+        <v>13345.3</v>
       </c>
     </row>
     <row r="696">
@@ -42915,7 +42915,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>16154.47</v>
+        <v>16644.32</v>
       </c>
     </row>
     <row r="697">
@@ -42976,7 +42976,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>15401.81</v>
+        <v>15868.84</v>
       </c>
     </row>
     <row r="698">
@@ -43037,7 +43037,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>912.73</v>
+        <v>940.4</v>
       </c>
     </row>
     <row r="699">
@@ -43098,7 +43098,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1167.95</v>
+        <v>1203.36</v>
       </c>
     </row>
     <row r="700">
@@ -43159,7 +43159,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>3069.35</v>
+        <v>3162.42</v>
       </c>
     </row>
     <row r="701">
@@ -43220,7 +43220,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>481.4</v>
+        <v>496</v>
       </c>
     </row>
     <row r="702">
@@ -43281,7 +43281,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>5200.12</v>
+        <v>5357.81</v>
       </c>
     </row>
     <row r="703">
@@ -43342,7 +43342,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>2472.74</v>
+        <v>2547.72</v>
       </c>
     </row>
     <row r="704">
@@ -43403,7 +43403,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>139.67</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="705">
@@ -43464,7 +43464,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>738.84</v>
+        <v>761.24</v>
       </c>
     </row>
     <row r="706">
@@ -43525,7 +43525,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>1098.99</v>
+        <v>1132.31</v>
       </c>
     </row>
     <row r="707">
@@ -43586,7 +43586,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>515.33</v>
+        <v>530.95</v>
       </c>
     </row>
     <row r="708">
@@ -43647,7 +43647,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>374.78</v>
+        <v>386.15</v>
       </c>
     </row>
     <row r="709">
@@ -43708,7 +43708,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1949.66</v>
+        <v>2008.78</v>
       </c>
     </row>
     <row r="710">
@@ -43769,7 +43769,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>496.08</v>
+        <v>511.12</v>
       </c>
     </row>
     <row r="711">
@@ -43830,7 +43830,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>2739.53</v>
+        <v>2822.6</v>
       </c>
     </row>
     <row r="712">
@@ -43891,7 +43891,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>22698.78</v>
+        <v>23387.08</v>
       </c>
     </row>
     <row r="713">
@@ -43952,7 +43952,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>3486.67</v>
+        <v>3592.4</v>
       </c>
     </row>
     <row r="714">
@@ -44013,7 +44013,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>449.09</v>
+        <v>462.44</v>
       </c>
     </row>
     <row r="715">
@@ -44074,7 +44074,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>3181.08</v>
+        <v>3275.64</v>
       </c>
     </row>
     <row r="716">
@@ -44135,7 +44135,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>116.78</v>
+        <v>120.25</v>
       </c>
     </row>
     <row r="717">
@@ -44196,7 +44196,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>259.82</v>
+        <v>267.54</v>
       </c>
     </row>
     <row r="718">
@@ -44257,7 +44257,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>938.5700000000001</v>
+        <v>966.47</v>
       </c>
     </row>
     <row r="719">
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>64.61</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="720">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>259.82</v>
+        <v>267.54</v>
       </c>
     </row>
     <row r="721">
@@ -44440,7 +44440,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>5369.63</v>
+        <v>5529.23</v>
       </c>
     </row>
     <row r="722">
@@ -44501,7 +44501,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>161.01</v>
+        <v>165.79</v>
       </c>
     </row>
     <row r="723">
@@ -44562,7 +44562,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>4504.74</v>
+        <v>4638.64</v>
       </c>
     </row>
     <row r="724">
@@ -44623,7 +44623,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>951.09</v>
+        <v>979.36</v>
       </c>
     </row>
     <row r="725">
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>208.39</v>
+        <v>214.59</v>
       </c>
     </row>
     <row r="726">
@@ -44745,7 +44745,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>1389.6</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="727">
@@ -44806,7 +44806,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>160.22</v>
+        <v>164.99</v>
       </c>
     </row>
     <row r="728">
@@ -44867,7 +44867,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>142.2</v>
+        <v>146.43</v>
       </c>
     </row>
     <row r="729">
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>143.77</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="730">
@@ -44989,7 +44989,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>71.09</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="731">
@@ -45050,7 +45050,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1316.82</v>
+        <v>1355.96</v>
       </c>
     </row>
     <row r="732">
@@ -45111,7 +45111,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>22614.45</v>
+        <v>23286.62</v>
       </c>
     </row>
     <row r="733">
@@ -45172,7 +45172,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>456.36</v>
+        <v>469.93</v>
       </c>
     </row>
     <row r="734">
@@ -45233,7 +45233,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>312.86</v>
+        <v>322.16</v>
       </c>
     </row>
     <row r="735">
@@ -45294,7 +45294,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>4119.39</v>
+        <v>4241.83</v>
       </c>
     </row>
     <row r="736">
@@ -45355,7 +45355,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>1125.32</v>
+        <v>1158.77</v>
       </c>
     </row>
     <row r="737">
@@ -45416,7 +45416,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>17298.47</v>
+        <v>17812.63</v>
       </c>
     </row>
     <row r="738">
@@ -45477,7 +45477,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>188.56</v>
+        <v>194.17</v>
       </c>
     </row>
     <row r="739">
@@ -45538,7 +45538,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>487.33</v>
+        <v>501.81</v>
       </c>
     </row>
     <row r="740">
@@ -45599,7 +45599,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>11354.44</v>
+        <v>11691.93</v>
       </c>
     </row>
     <row r="741">
@@ -45660,7 +45660,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>8238.780000000001</v>
+        <v>8483.66</v>
       </c>
     </row>
     <row r="742">
@@ -45721,7 +45721,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>115.1</v>
+        <v>118.52</v>
       </c>
     </row>
     <row r="743">
@@ -45782,7 +45782,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1223.06</v>
+        <v>1259.41</v>
       </c>
     </row>
     <row r="744">
@@ -45843,7 +45843,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>718.87</v>
+        <v>740.24</v>
       </c>
     </row>
     <row r="745">
@@ -45904,7 +45904,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2909.13</v>
+        <v>2995.6</v>
       </c>
     </row>
     <row r="746">
@@ -45965,7 +45965,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>8957.049999999999</v>
+        <v>9223.280000000001</v>
       </c>
     </row>
     <row r="747">
@@ -46026,7 +46026,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>328.42</v>
+        <v>338.18</v>
       </c>
     </row>
     <row r="748">
@@ -46087,7 +46087,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>749.5700000000001</v>
+        <v>771.85</v>
       </c>
     </row>
     <row r="749">
@@ -46148,7 +46148,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>327.94</v>
+        <v>337.68</v>
       </c>
     </row>
     <row r="750">
@@ -46209,7 +46209,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>5897.73</v>
+        <v>6073.03</v>
       </c>
     </row>
     <row r="751">
@@ -46270,7 +46270,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>831.2</v>
+        <v>855.9</v>
       </c>
     </row>
     <row r="752">
@@ -46331,7 +46331,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>571.87</v>
+        <v>588.87</v>
       </c>
     </row>
     <row r="753">
@@ -46392,7 +46392,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>287.55</v>
+        <v>296.1</v>
       </c>
     </row>
     <row r="754">
@@ -46453,7 +46453,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>1990.37</v>
+        <v>2049.53</v>
       </c>
     </row>
     <row r="755">
@@ -46514,7 +46514,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>33808.47</v>
+        <v>34813.36</v>
       </c>
     </row>
     <row r="756">
@@ -46575,7 +46575,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>1131.79</v>
+        <v>1165.43</v>
       </c>
     </row>
     <row r="757">
@@ -46636,7 +46636,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>5215.67</v>
+        <v>5370.7</v>
       </c>
     </row>
     <row r="758">
@@ -46697,7 +46697,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>8155.83</v>
+        <v>8398.25</v>
       </c>
     </row>
     <row r="759">
@@ -46758,7 +46758,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>456.36</v>
+        <v>469.93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30584,7 +30584,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31549,7 +31549,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32525,7 +32525,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32708,7 +32708,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32769,7 +32769,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32891,7 +32891,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -34050,7 +34050,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34294,7 +34294,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35575,7 +35575,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -36002,7 +36002,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36368,7 +36368,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36734,7 +36734,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39906,7 +39906,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40455,7 +40455,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40577,7 +40577,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40760,7 +40760,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40882,7 +40882,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -41553,7 +41553,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41919,7 +41919,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41980,7 +41980,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42224,7 +42224,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42346,7 +42346,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -43078,7 +43078,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44420,7 +44420,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46067,7 +46067,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46128,7 +46128,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46372,7 +46372,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +13107,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +13172,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13237,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13302,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13367,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13432,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13497,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13562,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13627,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13692,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13757,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13822,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13887,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13952,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +14017,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +14082,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +14147,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14212,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14277,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14342,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14407,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14472,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14537,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14602,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14667,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14732,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14797,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14862,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14927,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14992,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +15057,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +15122,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +15187,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15252,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15317,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15382,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15447,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15512,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15577,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15642,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15707,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15772,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15837,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15902,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15967,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +16032,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +16097,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +16162,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16227,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16292,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16357,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16422,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16487,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16552,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16617,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16682,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16747,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16812,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16877,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16942,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +17007,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +17072,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +17137,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +17202,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17267,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17332,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17397,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17462,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17527,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17592,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17657,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17722,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17787,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17852,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17917,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17982,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +18047,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +18112,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +18177,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +18242,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +18307,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18372,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18437,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18502,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18567,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +18632,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18697,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18762,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18827,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18892,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18957,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +19022,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +19087,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +19152,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +19217,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +19282,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19347,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19412,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19477,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19542,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19607,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19672,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19737,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19802,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19867,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19932,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19997,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +20062,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +20127,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +20192,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +20257,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +20322,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20387,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20452,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20517,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20582,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20647,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20712,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20777,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20842,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20972,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +21037,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +21102,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +21167,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19968,7 +21232,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +21297,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21362,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21427,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20212,7 +21492,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +21557,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21622,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21687,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21752,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21817,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21882,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21947,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +22012,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +22077,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20822,7 +22142,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +22207,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +22272,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +22337,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22402,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +22467,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22532,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +22597,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +22662,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22727,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22792,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22857,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22922,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21615,7 +22987,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +23052,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +23117,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +23182,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +23247,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +23312,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +23377,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23442,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23507,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23572,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +23637,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +23702,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23767,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23832,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23897,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23962,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +24027,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22652,7 +24092,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +24157,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +24222,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +24287,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22896,7 +24352,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +24417,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +24482,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +24547,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +24612,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +24677,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +24742,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23323,7 +24807,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23384,7 +24872,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24937,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +25002,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23567,7 +25067,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +25132,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23689,7 +25197,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +25262,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +25327,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +25392,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +25457,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +25522,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +25587,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +25652,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +25717,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25782,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25847,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25912,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24421,7 +25977,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +26042,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +26107,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +26172,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +26237,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24726,7 +26302,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +26367,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +26432,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +26497,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24970,7 +26562,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +26627,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +26692,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25153,7 +26757,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +26822,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +26887,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26952,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +27017,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +27082,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +27147,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +27212,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +27277,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25702,7 +27342,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +27407,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +27472,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25885,7 +27537,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +27602,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26007,7 +27667,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26068,7 +27732,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +27797,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +27862,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27927,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26312,7 +27992,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26373,7 +28057,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26434,7 +28122,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +28187,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +28252,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +28317,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +28382,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +28447,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +28512,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26861,7 +28577,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26922,7 +28642,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +28707,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +28772,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +28837,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27166,7 +28902,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27227,7 +28967,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27288,7 +29032,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +29097,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27410,7 +29162,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27471,7 +29227,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +29292,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27593,7 +29357,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27654,7 +29422,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27715,7 +29487,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +29552,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +29617,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +29682,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27959,7 +29747,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28020,7 +29812,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +29877,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +29942,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28203,7 +30007,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +30072,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +30137,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +30202,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +30267,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +30332,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +30397,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28630,7 +30462,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +30527,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28752,7 +30592,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28813,7 +30657,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +30722,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28935,7 +30787,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +30852,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30917,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30982,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29179,7 +31047,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29240,7 +31112,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29301,7 +31177,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29362,7 +31242,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +31307,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +31372,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29545,7 +31437,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +31502,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +31567,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +31632,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +31697,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29850,7 +31762,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +31827,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29972,7 +31892,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31957,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30159,7 +32087,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30220,7 +32152,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30281,7 +32217,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30342,7 +32282,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30403,7 +32347,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30464,7 +32412,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30525,7 +32477,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30586,7 +32542,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30647,7 +32607,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30708,7 +32672,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30769,7 +32737,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30830,7 +32802,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30891,7 +32867,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30952,7 +32932,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31013,7 +32997,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31074,7 +33062,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31135,7 +33127,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31196,7 +33192,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31257,7 +33257,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31318,7 +33322,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31379,7 +33387,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31440,7 +33452,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31501,7 +33517,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31562,7 +33582,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31623,7 +33647,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31684,7 +33712,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31745,7 +33777,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31806,7 +33842,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31867,7 +33907,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31928,7 +33972,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31989,7 +34037,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32050,7 +34102,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32111,7 +34167,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32172,7 +34232,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32233,7 +34297,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32294,7 +34362,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32355,7 +34427,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32416,7 +34492,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32477,7 +34557,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32538,7 +34622,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32599,7 +34687,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32660,7 +34752,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32721,7 +34817,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32782,7 +34882,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32843,7 +34947,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32904,7 +35012,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32965,7 +35077,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33026,7 +35142,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33087,7 +35207,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33148,7 +35272,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33209,7 +35337,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33270,7 +35402,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33331,7 +35467,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33392,7 +35532,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33453,7 +35597,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33514,7 +35662,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33575,7 +35727,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33636,7 +35792,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33697,7 +35857,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33758,7 +35922,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33819,7 +35987,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33880,7 +36052,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33941,7 +36117,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34002,7 +36182,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34063,7 +36247,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34124,7 +36312,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34185,7 +36377,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34246,7 +36442,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34307,7 +36507,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34368,7 +36572,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34429,7 +36637,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34490,7 +36702,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34551,7 +36767,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34612,7 +36832,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34673,7 +36897,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34734,7 +36962,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34795,7 +37027,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34856,7 +37092,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34917,7 +37157,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34978,7 +37222,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35039,7 +37287,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35100,7 +37352,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35161,7 +37417,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35222,7 +37482,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35283,7 +37547,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35344,7 +37612,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35405,7 +37677,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35466,7 +37742,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35527,7 +37807,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35588,7 +37872,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35649,7 +37937,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35710,7 +38002,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35771,7 +38067,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35832,7 +38132,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35893,7 +38197,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35954,7 +38262,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36015,7 +38327,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36076,7 +38392,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36137,7 +38457,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36198,7 +38522,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36259,7 +38587,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36320,7 +38652,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36381,7 +38717,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36442,7 +38782,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36503,7 +38847,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36564,7 +38912,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36625,7 +38977,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36686,7 +39042,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36747,7 +39107,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36808,7 +39172,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36869,7 +39237,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36930,7 +39302,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36991,7 +39367,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37052,7 +39432,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37113,7 +39497,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37174,7 +39562,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37235,7 +39627,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37296,7 +39692,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37357,7 +39757,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37418,7 +39822,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37479,7 +39887,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37540,7 +39952,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37601,7 +40017,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37662,7 +40082,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37723,7 +40147,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37784,7 +40212,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37845,7 +40277,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37906,7 +40342,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37967,7 +40407,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38028,7 +40472,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38089,7 +40537,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38150,7 +40602,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38211,7 +40667,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38272,7 +40732,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38333,7 +40797,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38394,7 +40862,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38455,7 +40927,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38516,7 +40992,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38577,7 +41057,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38638,7 +41122,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38699,7 +41187,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38760,7 +41252,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38821,7 +41317,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38882,7 +41382,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38943,7 +41447,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39004,7 +41512,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39065,7 +41577,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39126,7 +41642,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39187,7 +41707,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39248,7 +41772,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39309,7 +41837,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39370,7 +41902,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39431,7 +41967,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39492,7 +42032,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39553,7 +42097,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39614,7 +42162,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39675,7 +42227,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39736,7 +42292,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39797,7 +42357,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39858,7 +42422,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39919,7 +42487,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39980,7 +42552,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40041,7 +42617,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40102,7 +42682,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40163,7 +42747,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40224,7 +42812,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40285,7 +42877,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40346,7 +42942,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40407,7 +43007,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40468,7 +43072,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40529,7 +43137,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40590,7 +43202,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40651,7 +43267,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40712,7 +43332,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40773,7 +43397,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40834,7 +43462,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40895,7 +43527,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40956,7 +43592,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41017,7 +43657,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41078,7 +43722,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41139,7 +43787,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41200,7 +43852,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41261,7 +43917,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41322,7 +43982,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41383,7 +44047,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41444,7 +44112,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41505,7 +44177,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41566,7 +44242,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41627,7 +44307,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41688,7 +44372,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41749,7 +44437,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41810,7 +44502,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41871,7 +44567,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41932,7 +44632,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41993,7 +44697,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42054,7 +44762,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42115,7 +44827,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42176,7 +44892,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42237,7 +44957,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42298,7 +45022,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42359,7 +45087,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42420,7 +45152,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42481,7 +45217,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42542,7 +45282,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42603,7 +45347,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42664,7 +45412,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42725,7 +45477,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42786,7 +45542,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42847,7 +45607,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42908,7 +45672,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42969,7 +45737,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43030,7 +45802,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43091,7 +45867,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43152,7 +45932,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43213,7 +45997,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43274,7 +46062,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43335,7 +46127,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43396,7 +46192,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43457,7 +46257,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43518,7 +46322,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43579,7 +46387,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43640,7 +46452,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43701,7 +46517,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43762,7 +46582,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43823,7 +46647,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43884,7 +46712,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43945,7 +46777,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44006,7 +46842,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44067,7 +46907,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44128,7 +46972,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44189,7 +47037,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44250,7 +47102,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44311,7 +47167,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44372,7 +47232,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44433,7 +47297,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44494,7 +47362,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44555,7 +47427,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44616,7 +47492,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44677,7 +47557,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44738,7 +47622,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44799,7 +47687,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44860,7 +47752,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44921,7 +47817,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44982,7 +47882,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45043,7 +47947,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45104,7 +48012,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45165,7 +48077,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45226,7 +48142,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45287,7 +48207,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45348,7 +48272,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45409,7 +48337,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45470,7 +48402,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45531,7 +48467,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45592,7 +48532,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45653,7 +48597,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45714,7 +48662,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45775,7 +48727,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45836,7 +48792,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45897,7 +48857,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45958,7 +48922,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46019,7 +48987,11 @@
           <t>91.806.000-6</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46080,7 +49052,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46141,7 +49117,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46202,7 +49182,11 @@
           <t>96.568.740-8</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46263,7 +49247,11 @@
           <t>96.928.510-k</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/ene-2026.xlsx
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -36869,7 +36869,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
@@ -42329,7 +42329,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
